--- a/8th semester/DTTT- Digital Transformation; Tools and Technologies - Rafi Uddin & Komal Ridda/DTTT - Spring 26 - Project.xlsx
+++ b/8th semester/DTTT- Digital Transformation; Tools and Technologies - Rafi Uddin & Komal Ridda/DTTT - Spring 26 - Project.xlsx
@@ -1,36 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m_mus\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38B876F9-BC00-47FA-8BDC-4C4272E2E88C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Section A" sheetId="1" r:id="rId1"/>
-    <sheet name="Section B" sheetId="2" r:id="rId2"/>
+    <sheet state="visible" name="Mustajab" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Komal" sheetId="2" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="4fiN/4Z2jltmHS1Aut6oL+nWubO2VolhbqauglXsrgA="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="0gvKbH/i9gUrU3AyfTD7XxUzNwjP+fa+PEgpmfnkgEg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="177">
   <si>
     <t>Timing</t>
   </si>
   <si>
+    <t>Time</t>
+  </si>
+  <si>
     <t>Project Name</t>
   </si>
   <si>
@@ -52,43 +46,564 @@
     <t>Username</t>
   </si>
   <si>
-    <t>Internship Mangement System</t>
-  </si>
-  <si>
-    <t>A simple app to track student internships, supervisors, and company feedback.</t>
-  </si>
-  <si>
-    <t>Ayyan Ali (22k-5194)</t>
-  </si>
-  <si>
-    <t>Amal Abdul Rehman (22k-4822)</t>
-  </si>
-  <si>
-    <t>Ali Nazir (22k-5164)</t>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>10:00 AM – 10:15 AM</t>
+  </si>
+  <si>
+    <t>Ticket management system in Canvas App</t>
+  </si>
+  <si>
+    <t>A ticket management system built using a Canvas App that allows users to create, track, and manage support tickets. It streamlines issue reporting, assigns tickets to relevant personnel, and provides real time status updates for efficient resolution.</t>
+  </si>
+  <si>
+    <t>Jahantaab Kulsoom 22k-4214</t>
+  </si>
+  <si>
+    <t>Zaina Liaquat 22K-0506</t>
+  </si>
+  <si>
+    <t>Kousar Saeed 22K-4588</t>
+  </si>
+  <si>
+    <t>sectiona8@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>F@stbatch2026</t>
+  </si>
+  <si>
+    <t>10:15 AM – 10:30 AM</t>
+  </si>
+  <si>
+    <t>Student Complaint Management System</t>
+  </si>
+  <si>
+    <t>A Canvas App–based Student Complaint Management System that allows students to submit and track complaints while enabling administrators to manage and resolve issues with real-time status updates.</t>
+  </si>
+  <si>
+    <t>Raheen Siddiqui 22K-4216</t>
+  </si>
+  <si>
+    <t>Zehra Raza 22K-4197</t>
+  </si>
+  <si>
+    <t>Zoya Raza 22K-4194</t>
+  </si>
+  <si>
+    <t>Zoha Hussain 22K-4644</t>
+  </si>
+  <si>
+    <t>sectiona5@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>10:30 AM – 10:45 AM</t>
+  </si>
+  <si>
+    <t>Appointment Booking System</t>
+  </si>
+  <si>
+    <t>A Canvas App–based Appointment Booking System that enables users to schedule appointments by selecting available time slots while preventing double bookings, and allows administrators to manage schedules and approve bookings</t>
+  </si>
+  <si>
+    <t>Hazeen Dodhiya 22k4357</t>
+  </si>
+  <si>
+    <t>Owais Aamir 22k4322</t>
+  </si>
+  <si>
+    <t>sectiona4@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>10:45 AM – 11:00 AM</t>
+  </si>
+  <si>
+    <t>CareTrack (CMS &amp; PMS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinic staff manage patient records, doctor assignments, and appointments through a Model-Driven App, while patients use a Canvas App to register and check their appointment status </t>
+  </si>
+  <si>
+    <t>Talha Munir Saeed 22K-4465</t>
+  </si>
+  <si>
+    <t>Sahir Hassan 22K-4570</t>
+  </si>
+  <si>
+    <t>Umer Ali 22K-4398</t>
+  </si>
+  <si>
+    <t>sectiona9@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>11:00 AM – 11:15 AM</t>
+  </si>
+  <si>
+    <t>Library Management System</t>
+  </si>
+  <si>
+    <t>A Canvas App designed to manage book records, track availability, and handle borrowing activities for users and administrators. It provides a simple and flexible interface, can be extended with more features in future.</t>
+  </si>
+  <si>
+    <t>Syed Areeb Ashraf 22K-4243</t>
+  </si>
+  <si>
+    <t>Affan Hasan Khan 22K-4445</t>
+  </si>
+  <si>
+    <t>Ezaan Hussain 22K-4531</t>
+  </si>
+  <si>
+    <t>Muhammad Saad 22K-4407</t>
+  </si>
+  <si>
+    <t>sectiona1@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>11:15 AM – 11:30 AM</t>
+  </si>
+  <si>
+    <t>Petrol Subsidy Real-Time Tracking System</t>
+  </si>
+  <si>
+    <t>An app that digitally allocates fuel quotas and tracks real-time consumption via QR verification to reduce fraud and optimize subsidy usage</t>
+  </si>
+  <si>
+    <t>Muhammad Huzaifa 22k-4337</t>
+  </si>
+  <si>
+    <t>Shariq Nadeem 22k-4285</t>
+  </si>
+  <si>
+    <t>Ghulam Hussain 22k-4280</t>
+  </si>
+  <si>
+    <t>Anas Ahmed 22k-4154</t>
+  </si>
+  <si>
+    <t>sectiona7@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>11:30 AM – 11:45 AM</t>
+  </si>
+  <si>
+    <t>Smart Team Task and Approval Application</t>
+  </si>
+  <si>
+    <t>Canvas App that helps teams manage tasks, assign responsibilities, and streamline approval processes in a centralized system.</t>
+  </si>
+  <si>
+    <t>Syed Ashhal Hassan 22K-4306</t>
+  </si>
+  <si>
+    <t>Aawaiz Ali 22K-4573</t>
+  </si>
+  <si>
+    <t>Shuja ur Rahman 22K-4456</t>
+  </si>
+  <si>
+    <t>Hamza Siddiqui 22K-4245</t>
+  </si>
+  <si>
+    <t>sectiona6@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>11:45 AM – 12:00 PM</t>
+  </si>
+  <si>
+    <t>RiderFlow: Smart Delivery Management System</t>
+  </si>
+  <si>
+    <t>RiderFlow is a lightweight delivery management system designed for small businesses to efficiently manage orders and riders in real time 
+A canvas app that provides a centralized dashboard where admins can create and track orders, assign them to available riders, and monitor delivery progress</t>
+  </si>
+  <si>
+    <t>Uzair Khan 22K-4344</t>
+  </si>
+  <si>
+    <t>Zeefan Manzoor 22K-4650</t>
+  </si>
+  <si>
+    <t>Muneeb Maqsood 22K-4481</t>
+  </si>
+  <si>
+    <t>Murtaza Abbas 22K-4368</t>
+  </si>
+  <si>
+    <t>sectiona10@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>12:00 PM – 12:15 PM</t>
+  </si>
+  <si>
+    <t>PropPilot AI</t>
+  </si>
+  <si>
+    <t>AI-powered real estate CRM on Microsoft Dynamics 365 that automates property deal pipelines, agent assignment, commission calculation, and a Teams-integrated Copilot chatbot for natural language property management.</t>
+  </si>
+  <si>
+    <t>Anaksha Janki 22K-4293</t>
+  </si>
+  <si>
+    <t>Rania Ghazanfar 22K-4159</t>
+  </si>
+  <si>
+    <t>Marium Arif 22K-4320</t>
+  </si>
+  <si>
+    <t>sectiona3@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>12:15 PM – 12:30 PM</t>
+  </si>
+  <si>
+    <t>AI Facility &amp; Incident Management System</t>
+  </si>
+  <si>
+    <t>An AI-powered Facility &amp; Incident Management System built on Microsoft Power Platform using Canvas App, Dataverse, Power Automate, and Copilot integration. The system allows users to report maintenance and facility-related issues such as electrical faults, internet problems, classroom equipment issues, and other incidents. AI-based automation will categorize complaints, detect priority levels, assign them to the relevant department, and provide real-time status tracking with automated notifications and SLA monitoring.</t>
+  </si>
+  <si>
+    <t>K201899 Muhammad Shayan Shafique</t>
+  </si>
+  <si>
+    <t>12:30 PM – 12:45 PM</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>k224489@nu.edu.pk</t>
+  </si>
+  <si>
+    <t>k224148@nu.edu.pk</t>
+  </si>
+  <si>
+    <t>k220502@nu.edu.pk</t>
+  </si>
+  <si>
+    <t>k224637@nu.edu.pk</t>
+  </si>
+  <si>
+    <t>12:45 PM – 01:00 PM</t>
+  </si>
+  <si>
+    <t>Buffer Time</t>
+  </si>
+  <si>
+    <t>01:00 PM – 01:45 PM</t>
+  </si>
+  <si>
+    <t>Namaz &amp; Lunch Break</t>
+  </si>
+  <si>
+    <t>Expense Tracker App</t>
+  </si>
+  <si>
+    <t>A Power App with Power Automate workflow to automate expense submission, approval, and auditing. It provides a seamless experience for employees, approvers, and finance administrators with strong security and real-time visibility.</t>
+  </si>
+  <si>
+    <t>Hamza Ahmed 22K-5172</t>
+  </si>
+  <si>
+    <t>Abdullah Ellahi 22K-5190</t>
+  </si>
+  <si>
+    <t>Hassan Jamal 22K-5157</t>
+  </si>
+  <si>
+    <t>sectionb9@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>PowerJira</t>
+  </si>
+  <si>
+    <t>PowerJira is a team-based issue tracking and task management system built on Microsoft Power Platform. It allows teams to create projects, log issues, assign them to members with priority levels and due dates, and track their progress from open to resolved — all in one centralized app. The system eliminates manual follow-ups through automated email notifications that alert team members when a task is assigned to them and remind them when a deadline is approaching. Built using Power Apps as the front-end interface, Power Automate for workflow automation, and Dataverse as the backend data layer, PowerJira demonstrates how low-code tools can deliver a practical, real-world solution that improves team accountability, reduces missed deadlines, and enhances overall productivity.</t>
+  </si>
+  <si>
+    <t>Muhammad Sudais(22K-4364)</t>
+  </si>
+  <si>
+    <t>Munib Adil(22K-6006)</t>
+  </si>
+  <si>
+    <t>Nafay Zaki(22K-5104)</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>sectionb1@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Employee Leave Request &amp; Approval System</t>
+  </si>
+  <si>
+    <t>Employee submits leave → Power Automate sends approval email to manager → Manager approves/rejects → Employee gets notified automatically.</t>
+  </si>
+  <si>
+    <t>Falah Zainab (22k-4491)</t>
+  </si>
+  <si>
+    <t>Urwa Junaid (22k-4335)</t>
+  </si>
+  <si>
+    <t>Yusra Asim (22k-4378)</t>
+  </si>
+  <si>
+    <t>Abdul Rafey (22k-4182)</t>
+  </si>
+  <si>
+    <t>sectionb7@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Smart Cafeteria Pre-Order &amp; Pickup System</t>
+  </si>
+  <si>
+    <t>The Smart Cafeteria Pre-Order and Pickup System built using canvas app, simplifies campus food ordering by allowing students to place orders in advance, choose pickup times, and track order status. Cafeteria staff can manage and update orders efficiently.</t>
+  </si>
+  <si>
+    <t>Shaheer Beig (22K-4321)</t>
+  </si>
+  <si>
+    <t>Aliza Ashfaq (22K-4566)</t>
+  </si>
+  <si>
+    <t>Sayal Baig (22K-4625)</t>
+  </si>
+  <si>
+    <t>sectionb6@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Smart Retail &amp; Inventory ERP System</t>
+  </si>
+  <si>
+    <t>A digital transformation solution built on Microsoft Power Platform that automates retail operations including real-time product and stock management via Canvas App, and purchase order and supplier tracking via Model-Driven App — all connected through a centralised Microsoft Dataverse database.</t>
+  </si>
+  <si>
+    <t>Syed Azmeer Un Nabi(22K-4235)</t>
+  </si>
+  <si>
+    <t>Zain Baig(22K-4593)</t>
+  </si>
+  <si>
+    <t>Ashar Zamir(22K-4241)</t>
+  </si>
+  <si>
+    <t>sectionb8@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Inventory Management System</t>
+  </si>
+  <si>
+    <t>The project is an Inventory Management System consisting of two Power Apps. The Model-Driven App serves as the Admin portal for managing products, suppliers, stock levels, and inventory transactions. The Canvas App acts as the User/Buyer portal.</t>
+  </si>
+  <si>
+    <t>Rameen Rafiq (22k-5167)</t>
+  </si>
+  <si>
+    <t>Maham Farooqi (22k-4831)</t>
+  </si>
+  <si>
+    <t>Faiza Khan (22k-5160)</t>
+  </si>
+  <si>
+    <t>sectionb5@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Small business management system</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> An app that tracks inventory, raw materials, production progress, upcoming market stalls and online customer orders in all one place</t>
+  </si>
+  <si>
+    <t>Shanza Noor (22k-4870)</t>
+  </si>
+  <si>
+    <t>Hania Naseem (21k-4519)</t>
+  </si>
+  <si>
+    <t>Abdullah Arif (22k-5071)</t>
+  </si>
+  <si>
+    <t>sectionb11@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Expense Approval System</t>
+  </si>
+  <si>
+    <t>An application that allows users to submit expense requests, which are then processed through an approval chain, and maintains a complete audit trail of all decisions.</t>
+  </si>
+  <si>
+    <t>Sameer Ahmed (22k-5193)</t>
+  </si>
+  <si>
+    <t>Hamza (22k-4825)</t>
+  </si>
+  <si>
+    <t>Alizah Basit (22k-5155)</t>
+  </si>
+  <si>
+    <t>sectionb4@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Company Asset Issue &amp; Return Tracker</t>
+  </si>
+  <si>
+    <t>An app designed for HR and IT department to keep track of the items issued to employees. Automated flow to send emails about issue and status updates to relevant people</t>
+  </si>
+  <si>
+    <t>Taha Alam (22K-4425)</t>
+  </si>
+  <si>
+    <t>Muhammad Ashar (22K-4471)</t>
+  </si>
+  <si>
+    <t>sectionb10@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>AI-Powered Study Planner &amp; Productivity Tracker</t>
+  </si>
+  <si>
+    <t>A Canvas App on Microsoft Power Platform where students enter subjects, deadlines, and available study hours. Using Copilot, it generates a personalized daily study plan, tracks task completion, and calculates a productivity score based on performance. A real-time dashboard provides subject-wise trends and consistency insights for better academic decision-making.</t>
+  </si>
+  <si>
+    <t>Warisha Siddiqui  (22k-4186)</t>
+  </si>
+  <si>
+    <t>Taqwa Rasheed (22k-4557)</t>
+  </si>
+  <si>
+    <t>haneesh ali (22k-4260)</t>
+  </si>
+  <si>
+    <t>waniya syed (22k-4161)</t>
+  </si>
+  <si>
+    <t>sectionb2@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Internship Management System</t>
+  </si>
+  <si>
+    <t>A centralized, model-driven application built on Microsoft Power Apps and Dataverse that streamlines the entire internship lifecycle — managing student, company, and supervisor data in one place, with automated notifications, role-based access, and a real-time dashboard for progress tracking.</t>
+  </si>
+  <si>
+    <t>M.Abdullah Asif (22k-4560)</t>
+  </si>
+  <si>
+    <t>Muhammad Shaheer Ghouri (22k-4837)</t>
+  </si>
+  <si>
+    <t>sectionb3@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>Smart Maintenance Request &amp; SLA Management System:</t>
+  </si>
+  <si>
+    <t>A Canvas App–based system that allows users to submit and track maintenance requests while automatically assigning them to the relevant department based on category. It incorporates priority detection and SLA-based deadlines to ensure timely resolution and improve operational efficiency.</t>
+  </si>
+  <si>
+    <t>Adnan Sajid 22K-5175</t>
+  </si>
+  <si>
+    <t>M. Sadiq 22K-4303</t>
+  </si>
+  <si>
+    <t>Jamila Sohail 22k-4286</t>
+  </si>
+  <si>
+    <t>Amna Mubashir 22k-4342</t>
+  </si>
+  <si>
+    <t>sectiona2@28fzrb.onmicrosoft.com</t>
+  </si>
+  <si>
+    <t>01:45 PM – 02:00 PM</t>
+  </si>
+  <si>
+    <t>02:00 PM – 02:15 PM</t>
+  </si>
+  <si>
+    <t>02:15 PM – 02:30 PM</t>
+  </si>
+  <si>
+    <t>02:30 PM – 02:45 PM</t>
+  </si>
+  <si>
+    <t>02:45 PM – 03:00 PM</t>
+  </si>
+  <si>
+    <t>03:00 PM – 03:15 PM</t>
+  </si>
+  <si>
+    <t>03:15 PM – 03:30 PM</t>
+  </si>
+  <si>
+    <t>03:30 PM – 03:45 PM</t>
+  </si>
+  <si>
+    <t>03:45 PM – 04:00 PM</t>
+  </si>
+  <si>
+    <t>04:00 PM – 04:15 PM</t>
+  </si>
+  <si>
+    <t>04:15 PM – 04:45 PM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="10">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Ui-sans-serif"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+    </font>
+    <font/>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans&quot;"/>
     </font>
   </fonts>
   <fills count="3">
@@ -96,7 +611,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -105,14 +620,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="5">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -126,39 +635,117 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="21">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -348,102 +935,865 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="12.61328125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="41" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
-    <col min="3" max="3" width="133.23046875" customWidth="1"/>
-    <col min="4" max="7" width="35.84375" customWidth="1"/>
-    <col min="8" max="8" width="31.4609375" customWidth="1"/>
-    <col min="9" max="9" width="18.61328125" customWidth="1"/>
+    <col customWidth="1" hidden="1" min="1" max="1" width="41.0"/>
+    <col customWidth="1" min="2" max="2" width="17.13"/>
+    <col customWidth="1" min="3" max="3" width="46.13"/>
+    <col customWidth="1" min="4" max="4" width="219.13"/>
+    <col customWidth="1" min="5" max="8" width="35.88"/>
+    <col customWidth="1" min="9" max="9" width="31.5"/>
+    <col customWidth="1" min="10" max="10" width="18.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="5"/>
+      <c r="I10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="I12" s="5"/>
+      <c r="J12" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="9"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="C14:J14"/>
+    <mergeCell ref="C13:I13"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr defaultColWidth="12.61328125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="27.4609375" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="41.15234375" customWidth="1"/>
-    <col min="3" max="3" width="138" customWidth="1"/>
-    <col min="4" max="7" width="35.84375" customWidth="1"/>
-    <col min="8" max="8" width="35.4609375" customWidth="1"/>
+    <col customWidth="1" hidden="1" min="1" max="1" width="27.5"/>
+    <col customWidth="1" min="2" max="2" width="17.13"/>
+    <col customWidth="1" min="3" max="3" width="41.13"/>
+    <col customWidth="1" min="4" max="4" width="192.75"/>
+    <col customWidth="1" min="5" max="8" width="35.88"/>
+    <col customWidth="1" min="9" max="9" width="35.5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
+      <c r="P3" s="14"/>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+      <c r="S3" s="14"/>
+      <c r="T3" s="14"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="14"/>
+      <c r="W3" s="14"/>
+      <c r="X3" s="14"/>
+      <c r="Y3" s="14"/>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="14"/>
+      <c r="AB3" s="14"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="J9" s="12"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="J10" s="12"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="F13" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="20" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="20" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="20" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="20" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="20" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="20" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="20" t="s">
+        <v>176</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <mergeCells count="1">
+    <mergeCell ref="C14:J14"/>
+  </mergeCells>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>